--- a/data_analysis/data/mt_nucleoid_PTMs_list_P-sites_processed.xlsx
+++ b/data_analysis/data/mt_nucleoid_PTMs_list_P-sites_processed.xlsx
@@ -474,7 +474,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.946</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -546,7 +546,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.609,0.681</t>
+          <t>0.789,0.543</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.365,0.176,0.716</t>
+          <t>0.323,0.321,0.65</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.91,0.919,0.91</t>
+          <t>0.923,0.928,0.877</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.753,0.679,0.036,0.06</t>
+          <t>0.919,0.673,0.058,0.049</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.893,0.899,0.846,0.885,0.086</t>
+          <t>0.839,0.8,0.691,0.813,0.175</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -906,12 +906,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.355,0.256,0.28,0.126,0.114</t>
+          <t>0.571,0.356,0.341,0.078,0.074</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Ordered,Ordered,Ordered,Ordered,Ordered</t>
+          <t>Disordered,Ordered,Ordered,Ordered,Ordered</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.541,0.349,0.014,0.013,0.01,0.017</t>
+          <t>0.071,0.05,0.013,0.013,0.026,0.014</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Disordered,Ordered,Ordered,Ordered,Ordered,Ordered</t>
+          <t>Ordered,Ordered,Ordered,Ordered,Ordered,Ordered</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.294,0.086,0.037,0.24,0.44,0.46</t>
+          <t>0.071,0.052,0.043,0.22,0.161,0.126</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.073,0.057,0.231,0.312,0.022,0.62,0.988</t>
+          <t>0.153,0.148,0.367,0.383,0.198,0.847,0.98</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.912,0.033,0.013,0.009,0.323,0.421,0.245</t>
+          <t>0.887,0.035,0.029,0.02,0.184,0.177,0.138</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.132,0.14,0.041,0.025,0.083,0.077,0.01,0.011</t>
+          <t>0.227,0.172,0.139,0.076,0.185,0.135,0.078,0.065</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1338,12 +1338,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.85,0.838,0.817,0.412,0.219,0.041,0.044,0.121</t>
+          <t>0.964,0.958,0.871,0.703,0.623,0.054,0.068,0.061</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Disordered,Disordered,Disordered,Ordered,Ordered,Ordered,Ordered,Ordered</t>
+          <t>Disordered,Disordered,Disordered,Disordered,Disordered,Ordered,Ordered,Ordered</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.056,0.023,0.041,0.029,0.01,0.004,0.139,0.064,0.105,0.064</t>
+          <t>0.044,0.022,0.049,0.032,0.026,0.035,0.077,0.08,0.08,0.044</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.811,0.007,0.002,0.0,0.126,0.054,0.081,0.038,0.016,0,0.144</t>
+          <t>0.869,0.014,0.022,0.025,0.035,0.019,0.03,0.022,0.009,0.014,0.057</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.936,0.982,0.966,0.025,0.182,0.526,0.861,0.973,0.976,0.994,0.306</t>
+          <t>0.96,0.982,0.94,0.11,0.312,0.573,0.709,0.816,0.848,0.985,0.312</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.993,0.993,0.985,0.139,0.131,0.112,0.015,0.003,0.077,0.013,0.207,0.677</t>
+          <t>0.944,0.905,0.865,0.076,0.072,0.068,0.04,0.041,0.083,0.061,0.322,0.612</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.857,0.084,0.078,0.017,0.038,0.066,0.037,0.043,0.052,0.042,0.001,0.047</t>
+          <t>0.843,0.044,0.046,0.02,0.019,0.041,0.039,0.02,0.021,0.014,0.026,0.037</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.62,0.39,0.432,0.421,0.449,0.449,0.174,0.263,0.144,0.084,0.891,0.863</t>
+          <t>0.71,0.496,0.3,0.247,0.216,0.21,0.178,0.16,0.204,0.249,0.839,0.852</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.634,0.81,1,1,0.974,0.94,0.115,0.036,0.018,0.081,0.182,0.045,0.458</t>
+          <t>0.552,0.773,0.99,0.948,0.936,0.889,0.15,0.124,0.107,0.066,0.153,0.044,0.335</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.54,0.098,0.124,0.131,0.12,0.028,0.021,0.014,0.003,0.05,0.659,0.642,0.591</t>
+          <t>0.618,0.061,0.058,0.064,0.067,0.021,0.026,0.02,0.019,0.026,0.204,0.195,0.19</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Disordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Disordered,Disordered,Disordered</t>
+          <t>Disordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.933,0.944,0.935,0.935,0.92,0.901,0.914,0.907,0.882,0.874,0.858,0.739,0.491,0.043</t>
+          <t>0.973,0.976,0.959,0.967,0.975,0.935,0.904,0.846,0.78,0.729,0.701,0.6,0.484,0.03</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1,0.254,0.022,0.118,0.052,0.078,0.087,0.083,0.095,0.085,0.691,0.697,0.791,0.764</t>
+          <t>0.956,0.416,0.055,0.115,0.053,0.093,0.089,0.075,0.106,0.052,0.751,0.794,0.761,0.735</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.528,0.172,0.07,0.052,0.018,0.034,0.009,0.133,0.044,0.025,0.092,0.058,0.225,0.196,0.154</t>
+          <t>0.803,0.35,0.052,0.051,0.025,0.041,0.034,0.138,0.04,0.044,0.085,0.122,0.11,0.111,0.11</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2202,12 +2202,12 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.334,0.19,0.075,0.024,0.019,0.011,0.055,0.039,0.062,0.076,0.113,0.331,0.419,0.412,0.287,0.075</t>
+          <t>0.515,0.303,0.053,0.027,0.027,0.03,0.044,0.036,0.019,0.021,0.021,0.078,0.089,0.092,0.09,0.037</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered</t>
+          <t>Disordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.906,0.844,0.437,0.337,0.333,0.267,0.368,0.283,0.381,0.401,0.411,0.358,0.441,0.394,0.361,0.115,0.021</t>
+          <t>0.807,0.72,0.075,0.08,0.081,0.081,0.093,0.097,0.127,0.127,0.123,0.151,0.076,0.073,0.118,0.08,0.023</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.979,0.962,0.909,0.663,0.566,0.305,0.089,0.06,0.014,0.102,0.116,0.016,0.012,0.028,0.013,0.026,0.017,0</t>
+          <t>0.932,0.916,0.807,0.611,0.565,0.433,0.066,0.059,0.062,0.132,0.111,0.042,0.033,0.033,0.038,0.038,0.051,0.019</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.283,0.22,0.286,0.273,0.026,0.077,0.076,0.232,0.088,0.09,0.071,0.147,0.047,0.087,0.014,0.005,0.103,0.28,0.268,0.22</t>
+          <t>0.376,0.203,0.238,0.074,0.064,0.098,0.121,0.143,0.055,0.054,0.053,0.129,0.038,0.071,0.086,0.083,0.091,0.322,0.398,0.419</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.884,0.732,0,0,0.008,0.087,0.08,0.082,0.073,0.097,0.193,0.186,0.184,0.113,0.088,0.074,0.116,0.025,0.187,0.194</t>
+          <t>0.917,0.428,0.0,0.0,0.0,0.038,0.061,0.062,0.066,0.062,0.066,0.07,0.066,0.078,0.083,0.082,0.049,0.08,0.103,0.113</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Disordered,Disordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered</t>
+          <t>Disordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.827,0.773,0.822,0.835,0.833,0.84,0.859,0.917,0.909,0.819,0.973,0.969,0.97,0.972,0.958,0.981,0.912,0.851,0.381,0.033,0.015</t>
+          <t>0.918,0.917,0.93,0.928,0.952,0.968,0.957,0.976,0.976,0.949,0.985,0.981,0.987,0.981,0.948,0.936,0.777,0.718,0.403,0.034,0.034</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.994,0.907,0.874,0.558,0.326,0.263,0.247,0.014,0.176,0.022,0.239,0.157,0.015,0,0,0.121,0.039,0.114,0.027,0.013,0.027</t>
+          <t>0.916,0.805,0.79,0.627,0.558,0.526,0.233,0.048,0.101,0.042,0.1,0.099,0.023,0.024,0.064,0.101,0.033,0.065,0.065,0.08,0.123</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Disordered,Disordered,Disordered,Disordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered</t>
+          <t>Disordered,Disordered,Disordered,Disordered,Disordered,Disordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2706,12 +2706,12 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.962,0.871,0.541,0.223,0.216,0.358,0.309,0.858,0.897,0.912,0.927,0.931,0.929,0.953,0.959,0.95,0.673,0.646,0.794,0.594,0.822,0.869,0.214,0.137,0.059,0.053,0.004,0.051,0.023</t>
+          <t>0.911,0.85,0.657,0.517,0.453,0.41,0.557,0.849,0.875,0.898,0.922,0.932,0.944,0.963,0.948,0.839,0.48,0.363,0.364,0.526,0.641,0.665,0.144,0.092,0.076,0.071,0.066,0.077,0.058</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Disordered,Disordered,Disordered,Ordered,Ordered,Ordered,Ordered,Disordered,Disordered,Disordered,Disordered,Disordered,Disordered,Disordered,Disordered,Disordered,Disordered,Disordered,Disordered,Disordered,Disordered,Disordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered</t>
+          <t>Disordered,Disordered,Disordered,Disordered,Ordered,Ordered,Disordered,Disordered,Disordered,Disordered,Disordered,Disordered,Disordered,Disordered,Disordered,Disordered,Ordered,Ordered,Ordered,Disordered,Disordered,Disordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>1,0.972,0.835,0.092,0.092,0.102,0.033,0.033,0.025,0.025,0.031,0.016,0.059,0.056,0.043,0.016,0.009,0,0.058,0.072,0.064,0.054,0.046,0.046,0.085,0.065,0.057,0.034,0.026</t>
+          <t>0.904,0.899,0.758,0.078,0.073,0.035,0.026,0.024,0.024,0.021,0.024,0.01,0.016,0.015,0.014,0.018,0.021,0.024,0.033,0.032,0.031,0.03,0.05,0.058,0.09,0.081,0.079,0.092,0.043</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.469,0.443,0.059,0.001,0.003,0,0.037,0.053,0.045,0.052,0.053,0.029,0.059,0.017,0.012,0.018,0.085,0.079,0.091,0.088,0.082,0.073,0.051,0.032,0.093,0.074,0.08,0.124,0.203,0.179,0.163,0.066,0.049,0.069,0.099</t>
+          <t>0.809,0.768,0.22,0.017,0.009,0.002,0.022,0.019,0.02,0.017,0.018,0.018,0.019,0.009,0.009,0.009,0.02,0.036,0.033,0.034,0.038,0.036,0.035,0.021,0.02,0.053,0.056,0.052,0.132,0.135,0.11,0.029,0.027,0.037,0.18</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered</t>
+          <t>Disordered,Disordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>1,1,0.574,0.556,0.283,0.009,0.177,0.239,0.044,0.048,0.049,0.039,0.092,0.018,0.021,0.035,0.089,0.076,0.029,0.023,0.085,0.169,0.077,0.106,0.107,0.112,0.093,0.079,0.069,0.184,0.071,0.041,0.049,0.046,0.087</t>
+          <t>0.945,0.921,0.779,0.709,0.122,0.045,0.134,0.14,0.076,0.067,0.048,0.056,0.05,0.052,0.061,0.063,0.058,0.061,0.039,0.036,0.098,0.091,0.145,0.135,0.136,0.138,0.138,0.139,0.112,0.133,0.104,0.047,0.06,0.082,0.072</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.794,0.287,0.08,0.021,0,0,0.023,0.028,0.018,0.007,0.006,0.056,0.004,0.012,0.008,0.017,0.089,0.036,0.021,0.039,0.035,0.033,0.04,0.037,0.107,0.086,0.034,0.0,0.035,0.034,0.032,0.007,0.098,0.228,0.257,0.38,0.334,0.27,0.03</t>
+          <t>0.892,0.37,0.113,0.071,0.017,0.017,0.037,0.042,0.026,0.021,0.027,0.035,0.038,0.04,0.042,0.044,0.054,0.054,0.06,0.042,0.039,0.039,0.028,0.03,0.063,0.073,0.072,0.021,0.023,0.025,0.026,0.025,0.125,0.132,0.14,0.158,0.186,0.156,0.073</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3066,12 +3066,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.955,0.963,0.936,0.934,0.908,0.752,0.329,0.218,0.158,0.146,0.103,0.06,0.015,0.061,0.035,0.034,0.035,0.003,0.091,0.012,0.059,0.089,0.037,0.012,0.022,0.082,0.078,0.073,0.032,0.026,0.134,0.103,0.092,0.094,0.069,0.031,0.644,0.735,0.375,0.159,0.356,0.338,0.346,0.9,0.996</t>
+          <t>0.896,0.886,0.912,0.9,0.888,0.839,0.586,0.085,0.08,0.081,0.084,0.07,0.058,0.046,0.041,0.042,0.041,0.048,0.066,0.023,0.043,0.077,0.061,0.052,0.051,0.069,0.071,0.072,0.048,0.077,0.076,0.1,0.106,0.071,0.07,0.079,0.519,0.639,0.339,0.252,0.469,0.516,0.532,0.796,0.942</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Disordered,Disordered,Disordered,Disordered,Disordered,Disordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Disordered,Disordered,Ordered,Ordered,Ordered,Ordered,Ordered,Disordered,Disordered</t>
+          <t>Disordered,Disordered,Disordered,Disordered,Disordered,Disordered,Disordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Ordered,Disordered,Disordered,Ordered,Ordered,Ordered,Disordered,Disordered,Disordered,Disordered</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">

--- a/data_analysis/data/mt_nucleoid_PTMs_list_P-sites_processed.xlsx
+++ b/data_analysis/data/mt_nucleoid_PTMs_list_P-sites_processed.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N38"/>
+  <dimension ref="A1:P38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -422,6 +422,16 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>P-site RSA (%)</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>P-site Exposure</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>Annotation</t>
         </is>
       </c>
@@ -494,6 +504,16 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
+          <t>81.96</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Exposed</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
           <t>Mitochondrial ribosome-associated protein; regulates mitochondrial DNA copy number and the size and distribution of mtDNA nucleoids; subunit of a complex containing Pet20p, Mam33p, and Pim1p that may regulate mtDNA replication; member of the PET20 domain-containing protein family; forms foci that partially co-localize with mtDNA</t>
         </is>
       </c>
@@ -561,10 +581,20 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Exposed,Exposed</t>
+          <t>Exposed,Buried</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
+        <is>
+          <t>53.15,18.04</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Exposed,Buried</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>Mitochondrial membrane protein; coordinates expression of mitochondrially-encoded genes; may facilitate delivery of mRNA to membrane-bound translation machinery</t>
         </is>
@@ -638,6 +668,16 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
+          <t>66.43,46.15,37.76</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Exposed,Exposed,Exposed</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
           <t>Mitochondrial ribosomal protein of the small subunit</t>
         </is>
       </c>
@@ -710,6 +750,16 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
+          <t>86.71,73.43,88.81</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Exposed,Exposed,Exposed</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
           <t>Mitochondrial ribosomal protein of the large subunit; has similarity to E. coli L7/L12 and human MRPL7 ribosomal proteins; associates with the mitochondrial nucleoid; required for normal respiratory growth</t>
         </is>
       </c>
@@ -782,6 +832,16 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
+          <t>81.82,70.63,54.6,23.08</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Exposed,Exposed,Exposed,Exposed</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
           <t>Co-chaperone that stimulates HSP70 protein Ssc1p ATPase activity; involved in protein folding/refolding in the mitochodrial matrix; required for proteolysis of misfolded proteins; member of the HSP40 (DnaJ) family of chaperones</t>
         </is>
       </c>
@@ -849,10 +909,20 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Exposed,Exposed,Exposed,Exposed,Exposed</t>
+          <t>Exposed,Exposed,Exposed,Exposed,Buried</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
+        <is>
+          <t>82.82,76.07,53.85,34.97,17.48</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Exposed,Exposed,Exposed,Exposed,Buried</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
         <is>
           <t>Mitochondrial ribosomal protein of the large subunit</t>
         </is>
@@ -926,6 +996,16 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
+          <t>46.85,28.22,66.43,52.45,50.92</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Exposed,Exposed,Exposed,Exposed,Exposed</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
           <t>Mitochondrial matrix co-chaperonin; inhibits the ATPase activity of Hsp60p, a mitochondrial chaperonin; involved in protein folding and sorting in the mitochondria; 10 kD heat shock protein with similarity to E. coli groE</t>
         </is>
       </c>
@@ -993,10 +1073,20 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Buried,Exposed,Exposed,Exposed,Exposed,Exposed</t>
+          <t>Buried,Buried,Exposed,Exposed,Exposed,Exposed</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
+        <is>
+          <t>0.7,12.88,54.55,39.86,20.98,47.55</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Buried,Buried,Exposed,Exposed,Exposed,Exposed</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
         <is>
           <t>Catabolic L-serine (L-threonine) deaminase; catalyzes the degradation of both L-serine and L-threonine; required to use serine or threonine as the sole nitrogen source, transcriptionally induced by serine and threonine</t>
         </is>
@@ -1065,10 +1155,20 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Exposed,Exposed,Buried,Exposed,Exposed,Exposed</t>
+          <t>Buried,Exposed,Buried,Exposed,Buried,Exposed</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
+        <is>
+          <t>16.08,36.36,11.89,23.78,16.08,81.82</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Buried,Exposed,Buried,Exposed,Buried,Exposed</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
         <is>
           <t>Peroxisomal malate dehydrogenase; catalyzes interconversion of malate and oxaloacetate; involved in the glyoxylate cycle; mutation in human homolog MDH2 causes early-onset severe encephalopathy</t>
         </is>
@@ -1142,6 +1242,16 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
+          <t>24.54,6.13,4.29,44.17,0.61,77.62,76.22</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Exposed,Buried,Buried,Exposed,Buried,Exposed,Exposed</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
           <t>Mitochondrial DNA polymerase gamma; single subunit of mitochondrial DNA polymerase in yeast, in contrast to metazoan complex of catalytic and accessory subunits; polymorphic in yeast, petites occur more frequently in some lab strains; human ortholog POLG complements yeast mip1 mutant; mutations in human POLG associated with Alpers-Huttenlocher syndrome (AHS), progressive external ophthalmoplegia (PEO), parkinsonism, other mitochondrial diseases</t>
         </is>
       </c>
@@ -1214,6 +1324,16 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
+          <t>74.13,0,39.26,13.99,54.55,88.81,77.3</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Exposed,Buried,Exposed,Buried,Exposed,Exposed,Exposed</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
           <t>Citrate and oxoglutarate carrier protein; exports citrate from and imports oxoglutarate into the mitochondrion, causing net export of NADPH reducing equivalents; also associates with mt nucleoids and has a role in replication and segregation of the mt genome</t>
         </is>
       </c>
@@ -1286,6 +1406,16 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
+          <t>52.45,80.98,28.67,37.06,57.34,46.85,72.03,59.44</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
           <t>Mitochondrial DNA-binding protein; involved in mitochondrial DNA replication and recombination, member of HMG1 DNA-binding protein family; activity may be regulated by protein kinase A phosphorylation; ABF2 has a paralog, IXR1, that arose from the whole genome duplication; human homolog TFAM can complement yeast abf2 mutant, rescuing the loss-of-mitochondrial DNA phenotype</t>
         </is>
       </c>
@@ -1358,6 +1488,16 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
+          <t>79.02,84.66,72.73,50.35,71.17,1.18,5.59,36.2</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Buried,Exposed</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
           <t>NADH:ubiquinone oxidoreductase; transfers electrons from NADH to ubiquinone in respiratory chain but does not pump protons, in contrast to higher eukaryotic multisubunit respiratory complex I; upon apoptotic stress, is activated in mitochondria by N-terminal cleavage, then translocates to cytoplasm to induce apoptosis; homolog of human AIFM2; yeast NDI1 complements several phenotypes of human cell line with mutated MT-ND4, implicated in Leber hereditary optic neuropathy</t>
         </is>
       </c>
@@ -1425,10 +1565,20 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Exposed,Buried,Exposed,Exposed,Buried,Exposed,Exposed,Exposed,Buried,Buried</t>
+          <t>Exposed,Buried,Exposed,Exposed,Buried,Exposed,Buried,Exposed,Buried,Buried</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
+        <is>
+          <t>25.17,5.59,32.87,50.92,0,21.47,19.63,69.02,6.13,6.75</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Exposed,Buried,Exposed,Exposed,Buried,Exposed,Buried,Exposed,Buried,Buried</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
         <is>
           <t>E1 beta subunit of the pyruvate dehydrogenase (PDH) complex; PDH is an evolutionarily conserved multi-protein complex found in mitochondria</t>
         </is>
@@ -1497,10 +1647,20 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Exposed,Buried,Exposed,Buried,Exposed,Exposed,Buried,Exposed,Buried,Buried,Exposed</t>
+          <t>Exposed,Buried,Exposed,Buried,Buried,Buried,Buried,Exposed,Buried,Buried,Exposed</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
+        <is>
+          <t>72.03,0.61,20.25,4.9,17.48,17.79,6.29,44.06,7.69,3.07,26.57</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Exposed,Buried,Exposed,Buried,Buried,Buried,Buried,Exposed,Buried,Buried,Exposed</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
         <is>
           <t>Dihydrolipoamide dehydrogenase; the lipoamide dehydrogenase component (E3) of the pyruvate dehydrogenase and 2-oxoglutarate dehydrogenase multi-enzyme complexes; PDH complex is concentrated in spots within the mitochondrial matrix, often near the ERMES complex and near peroxisomes; LPD1 has a paralog, IRC15, that arose from the whole genome duplication</t>
         </is>
@@ -1574,6 +1734,16 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
+          <t>74.23,64.34,81.6,36.36,38.46,49.65,58.74,85.31,68.53,72.73,24.48</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
           <t>ATP-dependent Lon protease; involved in degradation of misfolded mitochondrial proteins; required for mitochondrial maintenance and biogenesis; regulates mitochondrial DNA copy number with Mrx6p; subunit of a complex containing Mrx6p, Pet20p, and Mam33p that may regulate mtDNA replication; protease-independent, chaperone-like function in mitochondrial membrane complex assembly; localizes to the mitochondrial matrix</t>
         </is>
       </c>
@@ -1641,10 +1811,20 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed</t>
+          <t>Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Buried,Exposed,Exposed,Exposed,Exposed,Exposed</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
+        <is>
+          <t>71.33,87.41,55.24,60.84,27.97,12.27,16.08,21.47,51.05,35.66,30.07,71.17</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Buried,Exposed,Exposed,Exposed,Exposed,Exposed</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
         <is>
           <t>Regulatory subunit of acetolactate synthase; acetolactate synthase catalyzes the first step of branched-chain amino acid biosynthesis; enhances activity of the Ilv2p catalytic subunit, localizes to mitochondria</t>
         </is>
@@ -1713,10 +1893,20 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Exposed,Buried</t>
+          <t>Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Buried,Exposed,Exposed,Buried,Buried,Buried</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
+        <is>
+          <t>76.22,32.52,55.24,8.59,42.94,24.48,15.34,40.39,34.97,11.89,17.48,7.36</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Buried,Exposed,Exposed,Buried,Buried,Buried</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
         <is>
           <t>Mitochondrial NADP-specific isocitrate dehydrogenase; catalyzes the oxidation of isocitrate to alpha-ketoglutarate; not required for mitochondrial respiration and may function to divert alpha-ketoglutarate to biosynthetic processes</t>
         </is>
@@ -1790,6 +1980,16 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
+          <t>77.3,40.56,25.87,39.88,57.67,30.07,6.29,10.49,41.72,23.08,58.04,68.53</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Buried,Exposed,Exposed,Exposed,Exposed</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
           <t>ssDNA-binding protein essential for mitochondrial genome maintenance; involved in mitochondrial DNA replication; stimulates utilization by Mip1p DNA polymerase of RNA primers synthesized by Rpo41p</t>
         </is>
       </c>
@@ -1862,6 +2062,16 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
+          <t>67.83,59.44,66.43,72.73,68.53,65.03,6.27,23.53,27.61,22.38,31.47,1.23,11.19</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Exposed,Exposed,Buried,Buried</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
           <t>Mitochondrial RNA polymerase; single subunit enzyme similar to those of T3 and T7 bacteriophages; requires a specificity subunit encoded by MTF1 for promoter recognition; Mtf1p interacts with and stabilizes the Rpo41p-promoter complex, enhancing DNA bending and melting to facilitate pre-initiation open complex formation; Rpo41p also synthesizes RNA primers for mitochondrial DNA replication</t>
         </is>
       </c>
@@ -1929,10 +2139,20 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Exposed,Exposed,Buried,Buried,Exposed,Exposed,Buried,Exposed,Buried,Buried,Exposed,Buried,Buried</t>
+          <t>Exposed,Exposed,Buried,Buried,Exposed,Buried,Buried,Exposed,Buried,Buried,Exposed,Buried,Buried</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
+        <is>
+          <t>70.55,22.38,3.07,7.69,39.86,16.08,4.29,20.25,0.7,4.2,81.12,9.79,13.29</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Exposed,Exposed,Buried,Buried,Exposed,Buried,Buried,Exposed,Buried,Buried,Exposed,Buried,Buried</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
         <is>
           <t>Subunit of mitochondrial NAD(+)-dependent isocitrate dehydrogenase; complex catalyzes the oxidation of isocitrate to alpha-ketoglutarate in the TCA cycle</t>
         </is>
@@ -2006,6 +2226,16 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
+          <t>77.3,65.03,71.33,61.54,80.42,34.97,64.34,60.74,73.62,60.84,90.8,77.62,74.83,72.73</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
           <t>Protein with a role in mitochondrial DNA recombinational repair; also involved in interstrand cross-link repair; binds to and catalyzes the annealing of single-stranded mtDNA; oligomerizes to form rings and filaments; related to Rad52-type recombination proteins, with limited overall similarity but sharing conserved functionally important residues; component of the mitochondrial nucleoid, required for the repair of oxidative mtDNA damage and mitochondrial genome maintenance</t>
         </is>
       </c>
@@ -2073,10 +2303,20 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Exposed,Buried,Exposed,Exposed,Buried,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed</t>
+          <t>Exposed,Buried,Exposed,Exposed,Buried,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Exposed</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
+        <is>
+          <t>83.92,9.82,73.43,60.14,6.99,47.55,32.87,32.87,43.36,35.58,77.62,79.72,19.58,64.42</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Exposed,Buried,Exposed,Exposed,Buried,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Exposed</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
         <is>
           <t>Acetylglutamate kinase and N-acetyl-gamma-glutamyl-phosphate reductase; N-acetyl-L-glutamate kinase (NAGK) catalyzes the 2nd and N-acetyl-gamma-glutamyl-phosphate reductase (NAGSA), the 3rd step in arginine biosynthesis; synthesized as a precursor which is processed in the mitochondrion to yield mature NAGK and NAGSA; enzymes form a metabolon complex with Arg2p; NAGK C-terminal domain stabilizes the enzymes, slows catalysis and is involved in feed-back inhibition by arginine</t>
         </is>
@@ -2145,10 +2385,20 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Exposed,Buried,Buried,Exposed,Buried,Exposed,Exposed,Exposed,Exposed,Buried,Exposed,Buried,Exposed,Exposed,Exposed</t>
+          <t>Exposed,Buried,Buried,Exposed,Buried,Buried,Exposed,Exposed,Exposed,Buried,Exposed,Buried,Exposed,Exposed,Exposed</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
+        <is>
+          <t>49.69,0,4.29,39.88,7.36,18.88,37.76,20.28,21.47,6.99,38.46,0,52.45,25.87,33.57</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Exposed,Buried,Buried,Exposed,Buried,Buried,Exposed,Exposed,Exposed,Buried,Exposed,Buried,Exposed,Exposed,Exposed</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
         <is>
           <t>Subunit 2 of ubiquinol cytochrome-c reductase (Complex III); Complex III is a component of the mitochondrial inner membrane electron transport chain; phosphorylated; transcription is regulated by Hap1p, Hap2p/Hap3p, and heme</t>
         </is>
@@ -2217,10 +2467,20 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Exposed,Buried,Exposed,Buried,Exposed,Buried,Exposed,Buried,Buried,Exposed,Exposed,Exposed,Exposed,Buried,Exposed,Exposed</t>
+          <t>Exposed,Buried,Buried,Buried,Exposed,Buried,Exposed,Buried,Buried,Buried,Exposed,Buried,Exposed,Buried,Exposed,Exposed</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
+        <is>
+          <t>65.73,0,14.11,7.69,60.74,1.23,25.15,0,0,18.86,94.41,15.38,82.52,7.36,28.67,35.66</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Exposed,Buried,Buried,Buried,Exposed,Buried,Exposed,Buried,Buried,Buried,Exposed,Buried,Exposed,Buried,Exposed,Exposed</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
         <is>
           <t>Alpha subunit of succinyl-CoA ligase; succinyl-CoA ligase is a mitochondrial enzyme of the TCA cycle that catalyzes the nucleotide-dependent conversion of succinyl-CoA to succinate; phosphorylated</t>
         </is>
@@ -2289,10 +2549,20 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Exposed,Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Buried,Exposed,Exposed,Exposed,Buried,Buried,Buried,Exposed,Buried,Exposed</t>
+          <t>Exposed,Exposed,Exposed,Exposed,Buried,Buried,Exposed,Buried,Exposed,Exposed,Exposed,Buried,Buried,Buried,Exposed,Buried,Exposed</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
+        <is>
+          <t>80.98,41.1,29.37,25.87,11.19,17.48,29.37,0,30.77,64.34,62.94,6.75,4.29,11.19,40.56,9.09,39.86</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Exposed,Exposed,Exposed,Exposed,Buried,Buried,Exposed,Buried,Exposed,Exposed,Exposed,Buried,Buried,Buried,Exposed,Buried,Exposed</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
         <is>
           <t>Core subunit of the ubiquinol-cytochrome c reductase complex; the ubiquinol-cytochrome c reductase complex (bc1 complex) is a component of the mitochondrial inner membrane electron transport chain</t>
         </is>
@@ -2361,10 +2631,20 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Exposed,Buried,Exposed,Buried,Exposed,Buried,Buried</t>
+          <t>Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Buried,Exposed,Exposed,Buried,Buried,Buried,Exposed,Buried,Buried</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
+        <is>
+          <t>70.55,63.64,76.92,84.62,55.83,26.38,34.97,29.37,0,18.88,39.86,26.99,7.69,15.38,2.1,21.47,12.59,0</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Buried,Exposed,Exposed,Buried,Buried,Buried,Exposed,Buried,Buried</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
         <is>
           <t>Beta subunit of the F1 sector of mitochondrial F1F0 ATP synthase; which is a large, evolutionarily conserved enzyme complex required for ATP synthesis; F1 translationally regulates ATP6 and ATP8 expression to achieve a balanced output of ATP synthase genes encoded in nucleus and mitochondria; phosphorylated</t>
         </is>
@@ -2438,6 +2718,16 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
+          <t>63.19,55.94,58.28,21.68,6.29,0,9.79,81.12,94.41,39.88,0,41.1,21.68,37.06,0,5.1,53.85,32.17,36.36,63.64</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Exposed,Exposed,Exposed,Exposed,Buried,Buried,Buried,Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Exposed,Buried,Buried,Exposed,Exposed,Exposed,Exposed</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
           <t>Subunit of the mitochondrial alpha-ketoglutarate dehydrogenase complex; catalyzes a key step in the tricarboxylic acid (TCA) cycle, the oxidative decarboxylation of alpha-ketoglutarate to form succinyl-CoA</t>
         </is>
       </c>
@@ -2505,10 +2795,20 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Exposed,Exposed,Exposed,Buried,Buried,Exposed,Exposed,Exposed,Exposed,Buried,Buried,Buried,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed</t>
+          <t>Exposed,Exposed,Buried,Buried,Buried,Buried,Exposed,Exposed,Exposed,Buried,Buried,Buried,Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Exposed,Exposed</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
+        <is>
+          <t>74.85,58.04,17.25,1.4,9.09,16.08,31.9,68.53,30.07,4.71,11.34,7.69,64.34,42.33,76.07,15.29,50.35,41.96,57.06,37.42</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Exposed,Exposed,Buried,Buried,Buried,Buried,Exposed,Exposed,Exposed,Buried,Buried,Buried,Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Exposed,Exposed</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
         <is>
           <t>E1 alpha subunit of the pyruvate dehydrogenase (PDH) complex; catalyzes the direct oxidative decarboxylation of pyruvate to acetyl-CoA; phosphorylated; regulated by glucose; PDH complex is concentrated in spots within the mitochondrial matrix, often near the ERMES complex and near peroxisomes</t>
         </is>
@@ -2577,10 +2877,20 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed</t>
+          <t>Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Buried</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
+        <is>
+          <t>30.07,60.84,77.62,87.73,78.32,83.53,79.02,39.16,28.22,0.7,77.62,72.73,83.22,85.89,85.28,78.32,76.22,69.23,77.3,17.18,19.63</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Buried</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
         <is>
           <t>Dihydrolipoyl transsuccinylase; component of the mitochondrial alpha-ketoglutarate dehydrogenase complex, which catalyzes the oxidative decarboxylation of alpha-ketoglutarate to succinyl-CoA in the TCA cycle; phosphorylated</t>
         </is>
@@ -2649,10 +2959,20 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Buried,Exposed,Buried,Exposed,Exposed,Exposed,Exposed,Exposed</t>
+          <t>Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Buried,Buried,Buried,Exposed,Exposed,Exposed,Exposed,Exposed</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
+        <is>
+          <t>67.13,39.16,93.87,11.66,70.63,40.56,63.64,43.36,59.44,28.83,82.52,47.55,6.13,12.59,16.78,13.99,40.56,81.12,68.53,30.77,44.76</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Buried,Buried,Buried,Exposed,Exposed,Exposed,Exposed,Exposed</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
         <is>
           <t>Alpha subunit of the F1 sector of mitochondrial F1F0 ATP synthase; which is a large, evolutionarily conserved enzyme complex required for ATP synthesis; F1 translationally regulates ATP6 and ATP8 expression to achieve a balanced output of ATP synthase genes encoded in nucleus and mitochondria; phosphorylated; N-terminally propionylated in viv</t>
         </is>
@@ -2721,10 +3041,20 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Buried,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Exposed,Buried,Exposed,Exposed</t>
+          <t>Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Buried,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Buried,Buried,Exposed,Exposed</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
+        <is>
+          <t>71.78,20.28,31.47,12.27,66.96,25.77,1.57,34.97,74.13,87.41,81.6,81.82,77.91,80.98,76.22,83.92,16.08,50.35,71.17,31.47,38.46,51.75,2.1,45.45,38.46,18.18,13.99,48.25,34.97</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Buried,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Buried,Buried,Exposed,Exposed</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
         <is>
           <t>Dihydrolipoamide acetyltransferase component (E2) of the PDC; the pyruvate dehydrogenase complex (PDC) catalyzes the oxidative decarboxylation of pyruvate to acetyl-CoA</t>
         </is>
@@ -2793,10 +3123,20 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Exposed,Buried,Buried,Buried,Buried,Exposed,Buried,Buried,Buried,Buried,Buried,Exposed,Buried,Exposed,Buried,Exposed,Exposed,Buried,Exposed,Exposed,Buried</t>
+          <t>Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Buried,Exposed,Buried,Buried,Buried,Buried,Exposed,Buried,Buried,Buried,Buried,Buried,Exposed,Buried,Exposed,Buried,Exposed,Exposed,Buried,Exposed,Exposed,Buried</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
+        <is>
+          <t>80.42,76.22,74.13,58.74,30.77,39.16,18.88,2.8,44.17,5.59,9.2,0,0,20.98,0,0,2.75,0,6.13,37.06,4.29,38.04,1.4,64.34,48.25,4.29,26.57,78.32,11.19</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Buried,Exposed,Buried,Buried,Buried,Buried,Exposed,Buried,Buried,Buried,Buried,Buried,Exposed,Buried,Exposed,Buried,Exposed,Exposed,Buried,Exposed,Exposed,Buried</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
         <is>
           <t>Mitochondrial aldehyde dehydrogenase; required for growth on ethanol and conversion of acetaldehyde to acetate; phosphorylated; activity is K+ dependent; utilizes NADP+ or NAD+ equally as coenzymes; expression is glucose repressed; can substitute for cytosolic NADP-dependent aldehyde dehydrogenase when directed to the cytosol; human homolog ALDH2 can complement yeast ald4 mutant</t>
         </is>
@@ -2865,10 +3205,20 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Exposed,Exposed,Buried,Buried,Buried,Buried,Buried,Exposed,Exposed,Buried,Buried,Exposed,Exposed,Buried,Buried,Exposed,Exposed,Buried,Buried,Buried,Buried,Buried,Buried,Buried,Buried,Buried,Buried,Exposed,Exposed,Exposed,Exposed,Buried,Buried,Exposed,Buried</t>
+          <t>Exposed,Exposed,Buried,Buried,Buried,Buried,Buried,Exposed,Exposed,Buried,Buried,Exposed,Exposed,Buried,Buried,Exposed,Buried,Buried,Buried,Buried,Buried,Buried,Buried,Buried,Buried,Buried,Buried,Exposed,Exposed,Exposed,Exposed,Buried,Buried,Exposed,Buried</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
+        <is>
+          <t>80.98,32.17,4.9,4.2,0,1.05,0,36.96,21.47,4.91,2.1,37.42,33.13,11.89,3.08,33.8,18.4,1.84,0.7,2.1,5.49,6.99,6.99,10.43,0.7,0,0,52.15,62.24,71.17,36.36,1.23,0,31.9,2.1</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Exposed,Exposed,Buried,Buried,Buried,Buried,Buried,Exposed,Exposed,Buried,Buried,Exposed,Exposed,Buried,Buried,Exposed,Buried,Buried,Buried,Buried,Buried,Buried,Buried,Buried,Buried,Buried,Buried,Exposed,Exposed,Exposed,Exposed,Buried,Buried,Exposed,Buried</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
         <is>
           <t>Aconitase; required for the tricarboxylic acid (TCA) cycle and also independently required for mitochondrial genome maintenance; component of the mitochondrial nucleoid; mutation leads to glutamate auxotrophy; human homolog ACO2 can complement yeast null mutant</t>
         </is>
@@ -2937,10 +3287,20 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Buried,Buried,Buried,Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Exposed,Exposed</t>
+          <t>Exposed,Exposed,Buried,Exposed,Exposed,Exposed,Buried,Buried,Buried,Buried,Buried,Exposed,Exposed,Exposed,Buried,Exposed,Buried,Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Exposed,Exposed,Buried,Buried,Exposed,Exposed,Exposed</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
+        <is>
+          <t>72.73,81.82,14.69,75.52,34.36,37.06,17.48,0,12.27,2.1,0.7,37.06,43.36,34.27,7.98,31.9,18.88,25.17,33.57,25.17,0,46.85,32.17,84.66,78.53,10.43,71.33,45.49,50.35,40.56,1.84,13.5,43.36,23.92,40.56</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Exposed,Exposed,Buried,Exposed,Exposed,Exposed,Buried,Buried,Buried,Buried,Buried,Exposed,Exposed,Exposed,Buried,Exposed,Buried,Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Exposed,Exposed,Buried,Buried,Exposed,Exposed,Exposed</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
         <is>
           <t>Tetradecameric mitochondrial chaperonin; required for ATP-dependent folding of precursor polypeptides and complex assembly; prevents aggregation and mediates protein refolding after heat shock; role in mtDNA transmission; phosphorylated</t>
         </is>
@@ -3009,10 +3369,20 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Buried,Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Buried,Buried,Buried,Exposed,Exposed,Exposed,Buried,Buried,Buried,Exposed,Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Buried,Exposed,Exposed,Exposed,Exposed</t>
+          <t>Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Buried,Exposed,Exposed,Exposed,Buried,Exposed,Buried,Buried,Buried,Buried,Exposed,Exposed,Exposed,Buried,Buried,Buried,Exposed,Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Buried,Exposed,Buried,Exposed,Exposed</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
+        <is>
+          <t>83.44,50.92,51.53,31.29,23.53,1.75,4.31,45.45,33.57,22.09,17.48,22.7,1.23,0,11.89,0,36.36,31.29,31.47,0,0,1.18,38.46,27.06,25.87,41.26,2.45,40,51.05,73.01,73.01,46.27,40,13.99,0,47.24,16.08,51.05,55.21</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Buried,Exposed,Exposed,Exposed,Buried,Exposed,Buried,Buried,Buried,Buried,Exposed,Exposed,Exposed,Buried,Buried,Buried,Exposed,Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Buried,Exposed,Buried,Exposed,Exposed</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
         <is>
           <t>Acetohydroxyacid reductoisomerase and mtDNA binding protein; involved in branched-chain amino acid biosynthesis and maintenance of wild-type mitochondrial DNA; found in mitochondrial nucleoids</t>
         </is>
@@ -3081,10 +3451,20 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Buried,Buried,Buried,Exposed,Exposed,Exposed,Buried,Buried,Buried,Buried,Exposed,Exposed,Buried,Exposed,Buried,Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Exposed,Exposed,Buried,Exposed,Exposed</t>
+          <t>Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Buried,Buried,Buried,Buried,Exposed,Buried,Exposed,Buried,Buried,Buried,Buried,Exposed,Exposed,Buried,Exposed,Buried,Exposed,Exposed,Exposed,Buried,Exposed,Buried,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Buried,Buried,Buried,Exposed,Exposed</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
+        <is>
+          <t>75.52,76.22,79.72,61.54,70.63,60.74,25.17,26.57,19.63,1.84,4.9,10.43,6.75,76.22,9.02,42.94,2.1,0,6.29,0.61,71.17,55.37,0.51,66.87,0,33.57,33.74,65.73,2.1,62.94,19.58,32.52,28.67,42.94,34.27,46.01,29.45,9.09,26.57,28.67,13.5,14.69,6.99,52.45,90.91</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Buried,Buried,Buried,Buried,Exposed,Buried,Exposed,Buried,Buried,Buried,Buried,Exposed,Exposed,Buried,Exposed,Buried,Exposed,Exposed,Exposed,Buried,Exposed,Buried,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Buried,Buried,Buried,Exposed,Exposed</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
         <is>
           <t>Hsp70 family ATPase; constituent of the import motor component of the Translocase of the Inner Mitochondrial membrane (TIM23 complex); involved in protein translocation and folding; subunit of SceI endonuclease; SSC1 has a paralog, ECM10, that arose from the whole genome duplication</t>
         </is>

--- a/data_analysis/data/mt_nucleoid_PTMs_list_P-sites_processed.xlsx
+++ b/data_analysis/data/mt_nucleoid_PTMs_list_P-sites_processed.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P38"/>
+  <dimension ref="A1:O38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -387,17 +387,17 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>P-site Functional STY (%)</t>
+          <t>P-site Functional Conservation (%)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>P-site pLDDT Score</t>
+          <t>P-site AF2 pLDDT Score</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>P-site Structural State</t>
+          <t>P-site AF2 Structural State</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -417,20 +417,15 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>P-site 3D Location (SASA)</t>
+          <t>P-site RSA (%)</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>P-site RSA (%)</t>
+          <t>P-site Exposure</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>P-site Exposure</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Annotation</t>
         </is>
@@ -499,20 +494,15 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>81.96</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>Exposed</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>81.96</t>
-        </is>
-      </c>
       <c r="O2" t="inlineStr">
-        <is>
-          <t>Exposed</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
         <is>
           <t>Mitochondrial ribosome-associated protein; regulates mitochondrial DNA copy number and the size and distribution of mtDNA nucleoids; subunit of a complex containing Pet20p, Mam33p, and Pim1p that may regulate mtDNA replication; member of the PET20 domain-containing protein family; forms foci that partially co-localize with mtDNA</t>
         </is>
@@ -581,20 +571,15 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>53.15,18.04</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>Exposed,Buried</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>53.15,18.04</t>
-        </is>
-      </c>
       <c r="O3" t="inlineStr">
-        <is>
-          <t>Exposed,Buried</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
         <is>
           <t>Mitochondrial membrane protein; coordinates expression of mitochondrially-encoded genes; may facilitate delivery of mRNA to membrane-bound translation machinery</t>
         </is>
@@ -663,20 +648,15 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>66.43,46.15,37.76</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>Exposed,Exposed,Exposed</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>66.43,46.15,37.76</t>
-        </is>
-      </c>
       <c r="O4" t="inlineStr">
-        <is>
-          <t>Exposed,Exposed,Exposed</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
         <is>
           <t>Mitochondrial ribosomal protein of the small subunit</t>
         </is>
@@ -745,20 +725,15 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>86.71,73.43,88.81</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>Exposed,Exposed,Exposed</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>86.71,73.43,88.81</t>
-        </is>
-      </c>
       <c r="O5" t="inlineStr">
-        <is>
-          <t>Exposed,Exposed,Exposed</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
         <is>
           <t>Mitochondrial ribosomal protein of the large subunit; has similarity to E. coli L7/L12 and human MRPL7 ribosomal proteins; associates with the mitochondrial nucleoid; required for normal respiratory growth</t>
         </is>
@@ -827,20 +802,15 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>81.82,70.63,54.6,23.08</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>Exposed,Exposed,Exposed,Exposed</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>81.82,70.63,54.6,23.08</t>
-        </is>
-      </c>
       <c r="O6" t="inlineStr">
-        <is>
-          <t>Exposed,Exposed,Exposed,Exposed</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
         <is>
           <t>Co-chaperone that stimulates HSP70 protein Ssc1p ATPase activity; involved in protein folding/refolding in the mitochodrial matrix; required for proteolysis of misfolded proteins; member of the HSP40 (DnaJ) family of chaperones</t>
         </is>
@@ -909,20 +879,15 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>82.82,76.07,53.85,34.97,17.48</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>Exposed,Exposed,Exposed,Exposed,Buried</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>82.82,76.07,53.85,34.97,17.48</t>
-        </is>
-      </c>
       <c r="O7" t="inlineStr">
-        <is>
-          <t>Exposed,Exposed,Exposed,Exposed,Buried</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
         <is>
           <t>Mitochondrial ribosomal protein of the large subunit</t>
         </is>
@@ -991,20 +956,15 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>46.85,28.22,66.43,52.45,50.92</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>Exposed,Exposed,Exposed,Exposed,Exposed</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>46.85,28.22,66.43,52.45,50.92</t>
-        </is>
-      </c>
       <c r="O8" t="inlineStr">
-        <is>
-          <t>Exposed,Exposed,Exposed,Exposed,Exposed</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
         <is>
           <t>Mitochondrial matrix co-chaperonin; inhibits the ATPase activity of Hsp60p, a mitochondrial chaperonin; involved in protein folding and sorting in the mitochondria; 10 kD heat shock protein with similarity to E. coli groE</t>
         </is>
@@ -1073,20 +1033,15 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>0.7,12.88,54.55,39.86,20.98,47.55</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
           <t>Buried,Buried,Exposed,Exposed,Exposed,Exposed</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0.7,12.88,54.55,39.86,20.98,47.55</t>
-        </is>
-      </c>
       <c r="O9" t="inlineStr">
-        <is>
-          <t>Buried,Buried,Exposed,Exposed,Exposed,Exposed</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
         <is>
           <t>Catabolic L-serine (L-threonine) deaminase; catalyzes the degradation of both L-serine and L-threonine; required to use serine or threonine as the sole nitrogen source, transcriptionally induced by serine and threonine</t>
         </is>
@@ -1155,20 +1110,15 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>16.08,36.36,11.89,23.78,16.08,81.82</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
           <t>Buried,Exposed,Buried,Exposed,Buried,Exposed</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>16.08,36.36,11.89,23.78,16.08,81.82</t>
-        </is>
-      </c>
       <c r="O10" t="inlineStr">
-        <is>
-          <t>Buried,Exposed,Buried,Exposed,Buried,Exposed</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
         <is>
           <t>Peroxisomal malate dehydrogenase; catalyzes interconversion of malate and oxaloacetate; involved in the glyoxylate cycle; mutation in human homolog MDH2 causes early-onset severe encephalopathy</t>
         </is>
@@ -1237,20 +1187,15 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
+          <t>24.54,6.13,4.29,44.17,0.61,77.62,76.22</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
           <t>Exposed,Buried,Buried,Exposed,Buried,Exposed,Exposed</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>24.54,6.13,4.29,44.17,0.61,77.62,76.22</t>
-        </is>
-      </c>
       <c r="O11" t="inlineStr">
-        <is>
-          <t>Exposed,Buried,Buried,Exposed,Buried,Exposed,Exposed</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
         <is>
           <t>Mitochondrial DNA polymerase gamma; single subunit of mitochondrial DNA polymerase in yeast, in contrast to metazoan complex of catalytic and accessory subunits; polymorphic in yeast, petites occur more frequently in some lab strains; human ortholog POLG complements yeast mip1 mutant; mutations in human POLG associated with Alpers-Huttenlocher syndrome (AHS), progressive external ophthalmoplegia (PEO), parkinsonism, other mitochondrial diseases</t>
         </is>
@@ -1319,20 +1264,15 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
+          <t>74.13,0,39.26,13.99,54.55,88.81,77.3</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
           <t>Exposed,Buried,Exposed,Buried,Exposed,Exposed,Exposed</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>74.13,0,39.26,13.99,54.55,88.81,77.3</t>
-        </is>
-      </c>
       <c r="O12" t="inlineStr">
-        <is>
-          <t>Exposed,Buried,Exposed,Buried,Exposed,Exposed,Exposed</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
         <is>
           <t>Citrate and oxoglutarate carrier protein; exports citrate from and imports oxoglutarate into the mitochondrion, causing net export of NADPH reducing equivalents; also associates with mt nucleoids and has a role in replication and segregation of the mt genome</t>
         </is>
@@ -1401,20 +1341,15 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
+          <t>52.45,80.98,28.67,37.06,57.34,46.85,72.03,59.44</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
           <t>Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>52.45,80.98,28.67,37.06,57.34,46.85,72.03,59.44</t>
-        </is>
-      </c>
       <c r="O13" t="inlineStr">
-        <is>
-          <t>Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
         <is>
           <t>Mitochondrial DNA-binding protein; involved in mitochondrial DNA replication and recombination, member of HMG1 DNA-binding protein family; activity may be regulated by protein kinase A phosphorylation; ABF2 has a paralog, IXR1, that arose from the whole genome duplication; human homolog TFAM can complement yeast abf2 mutant, rescuing the loss-of-mitochondrial DNA phenotype</t>
         </is>
@@ -1483,20 +1418,15 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
+          <t>79.02,84.66,72.73,50.35,71.17,1.18,5.59,36.2</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
           <t>Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Buried,Exposed</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>79.02,84.66,72.73,50.35,71.17,1.18,5.59,36.2</t>
-        </is>
-      </c>
       <c r="O14" t="inlineStr">
-        <is>
-          <t>Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Buried,Exposed</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
         <is>
           <t>NADH:ubiquinone oxidoreductase; transfers electrons from NADH to ubiquinone in respiratory chain but does not pump protons, in contrast to higher eukaryotic multisubunit respiratory complex I; upon apoptotic stress, is activated in mitochondria by N-terminal cleavage, then translocates to cytoplasm to induce apoptosis; homolog of human AIFM2; yeast NDI1 complements several phenotypes of human cell line with mutated MT-ND4, implicated in Leber hereditary optic neuropathy</t>
         </is>
@@ -1565,20 +1495,15 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
+          <t>25.17,5.59,32.87,50.92,0,21.47,19.63,69.02,6.13,6.75</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
           <t>Exposed,Buried,Exposed,Exposed,Buried,Exposed,Buried,Exposed,Buried,Buried</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>25.17,5.59,32.87,50.92,0,21.47,19.63,69.02,6.13,6.75</t>
-        </is>
-      </c>
       <c r="O15" t="inlineStr">
-        <is>
-          <t>Exposed,Buried,Exposed,Exposed,Buried,Exposed,Buried,Exposed,Buried,Buried</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
         <is>
           <t>E1 beta subunit of the pyruvate dehydrogenase (PDH) complex; PDH is an evolutionarily conserved multi-protein complex found in mitochondria</t>
         </is>
@@ -1647,20 +1572,15 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
+          <t>72.03,0.61,20.25,4.9,17.48,17.79,6.29,44.06,7.69,3.07,26.57</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
           <t>Exposed,Buried,Exposed,Buried,Buried,Buried,Buried,Exposed,Buried,Buried,Exposed</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>72.03,0.61,20.25,4.9,17.48,17.79,6.29,44.06,7.69,3.07,26.57</t>
-        </is>
-      </c>
       <c r="O16" t="inlineStr">
-        <is>
-          <t>Exposed,Buried,Exposed,Buried,Buried,Buried,Buried,Exposed,Buried,Buried,Exposed</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
         <is>
           <t>Dihydrolipoamide dehydrogenase; the lipoamide dehydrogenase component (E3) of the pyruvate dehydrogenase and 2-oxoglutarate dehydrogenase multi-enzyme complexes; PDH complex is concentrated in spots within the mitochondrial matrix, often near the ERMES complex and near peroxisomes; LPD1 has a paralog, IRC15, that arose from the whole genome duplication</t>
         </is>
@@ -1729,20 +1649,15 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
+          <t>74.23,64.34,81.6,36.36,38.46,49.65,58.74,85.31,68.53,72.73,24.48</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
           <t>Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>74.23,64.34,81.6,36.36,38.46,49.65,58.74,85.31,68.53,72.73,24.48</t>
-        </is>
-      </c>
       <c r="O17" t="inlineStr">
-        <is>
-          <t>Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
         <is>
           <t>ATP-dependent Lon protease; involved in degradation of misfolded mitochondrial proteins; required for mitochondrial maintenance and biogenesis; regulates mitochondrial DNA copy number with Mrx6p; subunit of a complex containing Mrx6p, Pet20p, and Mam33p that may regulate mtDNA replication; protease-independent, chaperone-like function in mitochondrial membrane complex assembly; localizes to the mitochondrial matrix</t>
         </is>
@@ -1811,20 +1726,15 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
+          <t>71.33,87.41,55.24,60.84,27.97,12.27,16.08,21.47,51.05,35.66,30.07,71.17</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
           <t>Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Buried,Exposed,Exposed,Exposed,Exposed,Exposed</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>71.33,87.41,55.24,60.84,27.97,12.27,16.08,21.47,51.05,35.66,30.07,71.17</t>
-        </is>
-      </c>
       <c r="O18" t="inlineStr">
-        <is>
-          <t>Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Buried,Exposed,Exposed,Exposed,Exposed,Exposed</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
         <is>
           <t>Regulatory subunit of acetolactate synthase; acetolactate synthase catalyzes the first step of branched-chain amino acid biosynthesis; enhances activity of the Ilv2p catalytic subunit, localizes to mitochondria</t>
         </is>
@@ -1893,20 +1803,15 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
+          <t>76.22,32.52,55.24,8.59,42.94,24.48,15.34,40.39,34.97,11.89,17.48,7.36</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
           <t>Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Buried,Exposed,Exposed,Buried,Buried,Buried</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>76.22,32.52,55.24,8.59,42.94,24.48,15.34,40.39,34.97,11.89,17.48,7.36</t>
-        </is>
-      </c>
       <c r="O19" t="inlineStr">
-        <is>
-          <t>Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Buried,Exposed,Exposed,Buried,Buried,Buried</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
         <is>
           <t>Mitochondrial NADP-specific isocitrate dehydrogenase; catalyzes the oxidation of isocitrate to alpha-ketoglutarate; not required for mitochondrial respiration and may function to divert alpha-ketoglutarate to biosynthetic processes</t>
         </is>
@@ -1975,20 +1880,15 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
+          <t>77.3,40.56,25.87,39.88,57.67,30.07,6.29,10.49,41.72,23.08,58.04,68.53</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
           <t>Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Buried,Exposed,Exposed,Exposed,Exposed</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>77.3,40.56,25.87,39.88,57.67,30.07,6.29,10.49,41.72,23.08,58.04,68.53</t>
-        </is>
-      </c>
       <c r="O20" t="inlineStr">
-        <is>
-          <t>Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Buried,Exposed,Exposed,Exposed,Exposed</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
         <is>
           <t>ssDNA-binding protein essential for mitochondrial genome maintenance; involved in mitochondrial DNA replication; stimulates utilization by Mip1p DNA polymerase of RNA primers synthesized by Rpo41p</t>
         </is>
@@ -2057,20 +1957,15 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
+          <t>67.83,59.44,66.43,72.73,68.53,65.03,6.27,23.53,27.61,22.38,31.47,1.23,11.19</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
           <t>Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Exposed,Exposed,Buried,Buried</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>67.83,59.44,66.43,72.73,68.53,65.03,6.27,23.53,27.61,22.38,31.47,1.23,11.19</t>
-        </is>
-      </c>
       <c r="O21" t="inlineStr">
-        <is>
-          <t>Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Exposed,Exposed,Buried,Buried</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
         <is>
           <t>Mitochondrial RNA polymerase; single subunit enzyme similar to those of T3 and T7 bacteriophages; requires a specificity subunit encoded by MTF1 for promoter recognition; Mtf1p interacts with and stabilizes the Rpo41p-promoter complex, enhancing DNA bending and melting to facilitate pre-initiation open complex formation; Rpo41p also synthesizes RNA primers for mitochondrial DNA replication</t>
         </is>
@@ -2139,20 +2034,15 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
+          <t>70.55,22.38,3.07,7.69,39.86,16.08,4.29,20.25,0.7,4.2,81.12,9.79,13.29</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
           <t>Exposed,Exposed,Buried,Buried,Exposed,Buried,Buried,Exposed,Buried,Buried,Exposed,Buried,Buried</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>70.55,22.38,3.07,7.69,39.86,16.08,4.29,20.25,0.7,4.2,81.12,9.79,13.29</t>
-        </is>
-      </c>
       <c r="O22" t="inlineStr">
-        <is>
-          <t>Exposed,Exposed,Buried,Buried,Exposed,Buried,Buried,Exposed,Buried,Buried,Exposed,Buried,Buried</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
         <is>
           <t>Subunit of mitochondrial NAD(+)-dependent isocitrate dehydrogenase; complex catalyzes the oxidation of isocitrate to alpha-ketoglutarate in the TCA cycle</t>
         </is>
@@ -2221,20 +2111,15 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
+          <t>77.3,65.03,71.33,61.54,80.42,34.97,64.34,60.74,73.62,60.84,90.8,77.62,74.83,72.73</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
           <t>Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>77.3,65.03,71.33,61.54,80.42,34.97,64.34,60.74,73.62,60.84,90.8,77.62,74.83,72.73</t>
-        </is>
-      </c>
       <c r="O23" t="inlineStr">
-        <is>
-          <t>Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
         <is>
           <t>Protein with a role in mitochondrial DNA recombinational repair; also involved in interstrand cross-link repair; binds to and catalyzes the annealing of single-stranded mtDNA; oligomerizes to form rings and filaments; related to Rad52-type recombination proteins, with limited overall similarity but sharing conserved functionally important residues; component of the mitochondrial nucleoid, required for the repair of oxidative mtDNA damage and mitochondrial genome maintenance</t>
         </is>
@@ -2303,20 +2188,15 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
+          <t>83.92,9.82,73.43,60.14,6.99,47.55,32.87,32.87,43.36,35.58,77.62,79.72,19.58,64.42</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
           <t>Exposed,Buried,Exposed,Exposed,Buried,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Exposed</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>83.92,9.82,73.43,60.14,6.99,47.55,32.87,32.87,43.36,35.58,77.62,79.72,19.58,64.42</t>
-        </is>
-      </c>
       <c r="O24" t="inlineStr">
-        <is>
-          <t>Exposed,Buried,Exposed,Exposed,Buried,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Exposed</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
         <is>
           <t>Acetylglutamate kinase and N-acetyl-gamma-glutamyl-phosphate reductase; N-acetyl-L-glutamate kinase (NAGK) catalyzes the 2nd and N-acetyl-gamma-glutamyl-phosphate reductase (NAGSA), the 3rd step in arginine biosynthesis; synthesized as a precursor which is processed in the mitochondrion to yield mature NAGK and NAGSA; enzymes form a metabolon complex with Arg2p; NAGK C-terminal domain stabilizes the enzymes, slows catalysis and is involved in feed-back inhibition by arginine</t>
         </is>
@@ -2385,20 +2265,15 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
+          <t>49.69,0,4.29,39.88,7.36,18.88,37.76,20.28,21.47,6.99,38.46,0,52.45,25.87,33.57</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
           <t>Exposed,Buried,Buried,Exposed,Buried,Buried,Exposed,Exposed,Exposed,Buried,Exposed,Buried,Exposed,Exposed,Exposed</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>49.69,0,4.29,39.88,7.36,18.88,37.76,20.28,21.47,6.99,38.46,0,52.45,25.87,33.57</t>
-        </is>
-      </c>
       <c r="O25" t="inlineStr">
-        <is>
-          <t>Exposed,Buried,Buried,Exposed,Buried,Buried,Exposed,Exposed,Exposed,Buried,Exposed,Buried,Exposed,Exposed,Exposed</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
         <is>
           <t>Subunit 2 of ubiquinol cytochrome-c reductase (Complex III); Complex III is a component of the mitochondrial inner membrane electron transport chain; phosphorylated; transcription is regulated by Hap1p, Hap2p/Hap3p, and heme</t>
         </is>
@@ -2467,20 +2342,15 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
+          <t>65.73,0,14.11,7.69,60.74,1.23,25.15,0,0,18.86,94.41,15.38,82.52,7.36,28.67,35.66</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
           <t>Exposed,Buried,Buried,Buried,Exposed,Buried,Exposed,Buried,Buried,Buried,Exposed,Buried,Exposed,Buried,Exposed,Exposed</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>65.73,0,14.11,7.69,60.74,1.23,25.15,0,0,18.86,94.41,15.38,82.52,7.36,28.67,35.66</t>
-        </is>
-      </c>
       <c r="O26" t="inlineStr">
-        <is>
-          <t>Exposed,Buried,Buried,Buried,Exposed,Buried,Exposed,Buried,Buried,Buried,Exposed,Buried,Exposed,Buried,Exposed,Exposed</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
         <is>
           <t>Alpha subunit of succinyl-CoA ligase; succinyl-CoA ligase is a mitochondrial enzyme of the TCA cycle that catalyzes the nucleotide-dependent conversion of succinyl-CoA to succinate; phosphorylated</t>
         </is>
@@ -2549,20 +2419,15 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
+          <t>80.98,41.1,29.37,25.87,11.19,17.48,29.37,0,30.77,64.34,62.94,6.75,4.29,11.19,40.56,9.09,39.86</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
           <t>Exposed,Exposed,Exposed,Exposed,Buried,Buried,Exposed,Buried,Exposed,Exposed,Exposed,Buried,Buried,Buried,Exposed,Buried,Exposed</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>80.98,41.1,29.37,25.87,11.19,17.48,29.37,0,30.77,64.34,62.94,6.75,4.29,11.19,40.56,9.09,39.86</t>
-        </is>
-      </c>
       <c r="O27" t="inlineStr">
-        <is>
-          <t>Exposed,Exposed,Exposed,Exposed,Buried,Buried,Exposed,Buried,Exposed,Exposed,Exposed,Buried,Buried,Buried,Exposed,Buried,Exposed</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
         <is>
           <t>Core subunit of the ubiquinol-cytochrome c reductase complex; the ubiquinol-cytochrome c reductase complex (bc1 complex) is a component of the mitochondrial inner membrane electron transport chain</t>
         </is>
@@ -2631,20 +2496,15 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
+          <t>70.55,63.64,76.92,84.62,55.83,26.38,34.97,29.37,0,18.88,39.86,26.99,7.69,15.38,2.1,21.47,12.59,0</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
           <t>Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Buried,Exposed,Exposed,Buried,Buried,Buried,Exposed,Buried,Buried</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>70.55,63.64,76.92,84.62,55.83,26.38,34.97,29.37,0,18.88,39.86,26.99,7.69,15.38,2.1,21.47,12.59,0</t>
-        </is>
-      </c>
       <c r="O28" t="inlineStr">
-        <is>
-          <t>Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Buried,Exposed,Exposed,Buried,Buried,Buried,Exposed,Buried,Buried</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
         <is>
           <t>Beta subunit of the F1 sector of mitochondrial F1F0 ATP synthase; which is a large, evolutionarily conserved enzyme complex required for ATP synthesis; F1 translationally regulates ATP6 and ATP8 expression to achieve a balanced output of ATP synthase genes encoded in nucleus and mitochondria; phosphorylated</t>
         </is>
@@ -2713,20 +2573,15 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
+          <t>63.19,55.94,58.28,21.68,6.29,0,9.79,81.12,94.41,39.88,0,41.1,21.68,37.06,0,5.1,53.85,32.17,36.36,63.64</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
           <t>Exposed,Exposed,Exposed,Exposed,Buried,Buried,Buried,Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Exposed,Buried,Buried,Exposed,Exposed,Exposed,Exposed</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>63.19,55.94,58.28,21.68,6.29,0,9.79,81.12,94.41,39.88,0,41.1,21.68,37.06,0,5.1,53.85,32.17,36.36,63.64</t>
-        </is>
-      </c>
       <c r="O29" t="inlineStr">
-        <is>
-          <t>Exposed,Exposed,Exposed,Exposed,Buried,Buried,Buried,Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Exposed,Buried,Buried,Exposed,Exposed,Exposed,Exposed</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
         <is>
           <t>Subunit of the mitochondrial alpha-ketoglutarate dehydrogenase complex; catalyzes a key step in the tricarboxylic acid (TCA) cycle, the oxidative decarboxylation of alpha-ketoglutarate to form succinyl-CoA</t>
         </is>
@@ -2795,20 +2650,15 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
+          <t>74.85,58.04,17.25,1.4,9.09,16.08,31.9,68.53,30.07,4.71,11.34,7.69,64.34,42.33,76.07,15.29,50.35,41.96,57.06,37.42</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
           <t>Exposed,Exposed,Buried,Buried,Buried,Buried,Exposed,Exposed,Exposed,Buried,Buried,Buried,Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Exposed,Exposed</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>74.85,58.04,17.25,1.4,9.09,16.08,31.9,68.53,30.07,4.71,11.34,7.69,64.34,42.33,76.07,15.29,50.35,41.96,57.06,37.42</t>
-        </is>
-      </c>
       <c r="O30" t="inlineStr">
-        <is>
-          <t>Exposed,Exposed,Buried,Buried,Buried,Buried,Exposed,Exposed,Exposed,Buried,Buried,Buried,Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Exposed,Exposed</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
         <is>
           <t>E1 alpha subunit of the pyruvate dehydrogenase (PDH) complex; catalyzes the direct oxidative decarboxylation of pyruvate to acetyl-CoA; phosphorylated; regulated by glucose; PDH complex is concentrated in spots within the mitochondrial matrix, often near the ERMES complex and near peroxisomes</t>
         </is>
@@ -2877,20 +2727,15 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
+          <t>30.07,60.84,77.62,87.73,78.32,83.53,79.02,39.16,28.22,0.7,77.62,72.73,83.22,85.89,85.28,78.32,76.22,69.23,77.3,17.18,19.63</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
           <t>Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Buried</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>30.07,60.84,77.62,87.73,78.32,83.53,79.02,39.16,28.22,0.7,77.62,72.73,83.22,85.89,85.28,78.32,76.22,69.23,77.3,17.18,19.63</t>
-        </is>
-      </c>
       <c r="O31" t="inlineStr">
-        <is>
-          <t>Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Buried</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
         <is>
           <t>Dihydrolipoyl transsuccinylase; component of the mitochondrial alpha-ketoglutarate dehydrogenase complex, which catalyzes the oxidative decarboxylation of alpha-ketoglutarate to succinyl-CoA in the TCA cycle; phosphorylated</t>
         </is>
@@ -2959,20 +2804,15 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
+          <t>67.13,39.16,93.87,11.66,70.63,40.56,63.64,43.36,59.44,28.83,82.52,47.55,6.13,12.59,16.78,13.99,40.56,81.12,68.53,30.77,44.76</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
           <t>Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Buried,Buried,Buried,Exposed,Exposed,Exposed,Exposed,Exposed</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>67.13,39.16,93.87,11.66,70.63,40.56,63.64,43.36,59.44,28.83,82.52,47.55,6.13,12.59,16.78,13.99,40.56,81.12,68.53,30.77,44.76</t>
-        </is>
-      </c>
       <c r="O32" t="inlineStr">
-        <is>
-          <t>Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Buried,Buried,Buried,Exposed,Exposed,Exposed,Exposed,Exposed</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
         <is>
           <t>Alpha subunit of the F1 sector of mitochondrial F1F0 ATP synthase; which is a large, evolutionarily conserved enzyme complex required for ATP synthesis; F1 translationally regulates ATP6 and ATP8 expression to achieve a balanced output of ATP synthase genes encoded in nucleus and mitochondria; phosphorylated; N-terminally propionylated in viv</t>
         </is>
@@ -3041,20 +2881,15 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
+          <t>71.78,20.28,31.47,12.27,66.96,25.77,1.57,34.97,74.13,87.41,81.6,81.82,77.91,80.98,76.22,83.92,16.08,50.35,71.17,31.47,38.46,51.75,2.1,45.45,38.46,18.18,13.99,48.25,34.97</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
           <t>Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Buried,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Buried,Buried,Exposed,Exposed</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>71.78,20.28,31.47,12.27,66.96,25.77,1.57,34.97,74.13,87.41,81.6,81.82,77.91,80.98,76.22,83.92,16.08,50.35,71.17,31.47,38.46,51.75,2.1,45.45,38.46,18.18,13.99,48.25,34.97</t>
-        </is>
-      </c>
       <c r="O33" t="inlineStr">
-        <is>
-          <t>Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Buried,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Buried,Buried,Exposed,Exposed</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
         <is>
           <t>Dihydrolipoamide acetyltransferase component (E2) of the PDC; the pyruvate dehydrogenase complex (PDC) catalyzes the oxidative decarboxylation of pyruvate to acetyl-CoA</t>
         </is>
@@ -3123,20 +2958,15 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
+          <t>80.42,76.22,74.13,58.74,30.77,39.16,18.88,2.8,44.17,5.59,9.2,0,0,20.98,0,0,2.75,0,6.13,37.06,4.29,38.04,1.4,64.34,48.25,4.29,26.57,78.32,11.19</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
           <t>Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Buried,Exposed,Buried,Buried,Buried,Buried,Exposed,Buried,Buried,Buried,Buried,Buried,Exposed,Buried,Exposed,Buried,Exposed,Exposed,Buried,Exposed,Exposed,Buried</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>80.42,76.22,74.13,58.74,30.77,39.16,18.88,2.8,44.17,5.59,9.2,0,0,20.98,0,0,2.75,0,6.13,37.06,4.29,38.04,1.4,64.34,48.25,4.29,26.57,78.32,11.19</t>
-        </is>
-      </c>
       <c r="O34" t="inlineStr">
-        <is>
-          <t>Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Buried,Exposed,Buried,Buried,Buried,Buried,Exposed,Buried,Buried,Buried,Buried,Buried,Exposed,Buried,Exposed,Buried,Exposed,Exposed,Buried,Exposed,Exposed,Buried</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
         <is>
           <t>Mitochondrial aldehyde dehydrogenase; required for growth on ethanol and conversion of acetaldehyde to acetate; phosphorylated; activity is K+ dependent; utilizes NADP+ or NAD+ equally as coenzymes; expression is glucose repressed; can substitute for cytosolic NADP-dependent aldehyde dehydrogenase when directed to the cytosol; human homolog ALDH2 can complement yeast ald4 mutant</t>
         </is>
@@ -3205,20 +3035,15 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
+          <t>80.98,32.17,4.9,4.2,0,1.05,0,36.96,21.47,4.91,2.1,37.42,33.13,11.89,3.08,33.8,18.4,1.84,0.7,2.1,5.49,6.99,6.99,10.43,0.7,0,0,52.15,62.24,71.17,36.36,1.23,0,31.9,2.1</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
           <t>Exposed,Exposed,Buried,Buried,Buried,Buried,Buried,Exposed,Exposed,Buried,Buried,Exposed,Exposed,Buried,Buried,Exposed,Buried,Buried,Buried,Buried,Buried,Buried,Buried,Buried,Buried,Buried,Buried,Exposed,Exposed,Exposed,Exposed,Buried,Buried,Exposed,Buried</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>80.98,32.17,4.9,4.2,0,1.05,0,36.96,21.47,4.91,2.1,37.42,33.13,11.89,3.08,33.8,18.4,1.84,0.7,2.1,5.49,6.99,6.99,10.43,0.7,0,0,52.15,62.24,71.17,36.36,1.23,0,31.9,2.1</t>
-        </is>
-      </c>
       <c r="O35" t="inlineStr">
-        <is>
-          <t>Exposed,Exposed,Buried,Buried,Buried,Buried,Buried,Exposed,Exposed,Buried,Buried,Exposed,Exposed,Buried,Buried,Exposed,Buried,Buried,Buried,Buried,Buried,Buried,Buried,Buried,Buried,Buried,Buried,Exposed,Exposed,Exposed,Exposed,Buried,Buried,Exposed,Buried</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
         <is>
           <t>Aconitase; required for the tricarboxylic acid (TCA) cycle and also independently required for mitochondrial genome maintenance; component of the mitochondrial nucleoid; mutation leads to glutamate auxotrophy; human homolog ACO2 can complement yeast null mutant</t>
         </is>
@@ -3287,20 +3112,15 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
+          <t>72.73,81.82,14.69,75.52,34.36,37.06,17.48,0,12.27,2.1,0.7,37.06,43.36,34.27,7.98,31.9,18.88,25.17,33.57,25.17,0,46.85,32.17,84.66,78.53,10.43,71.33,45.49,50.35,40.56,1.84,13.5,43.36,23.92,40.56</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
           <t>Exposed,Exposed,Buried,Exposed,Exposed,Exposed,Buried,Buried,Buried,Buried,Buried,Exposed,Exposed,Exposed,Buried,Exposed,Buried,Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Exposed,Exposed,Buried,Buried,Exposed,Exposed,Exposed</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>72.73,81.82,14.69,75.52,34.36,37.06,17.48,0,12.27,2.1,0.7,37.06,43.36,34.27,7.98,31.9,18.88,25.17,33.57,25.17,0,46.85,32.17,84.66,78.53,10.43,71.33,45.49,50.35,40.56,1.84,13.5,43.36,23.92,40.56</t>
-        </is>
-      </c>
       <c r="O36" t="inlineStr">
-        <is>
-          <t>Exposed,Exposed,Buried,Exposed,Exposed,Exposed,Buried,Buried,Buried,Buried,Buried,Exposed,Exposed,Exposed,Buried,Exposed,Buried,Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Exposed,Exposed,Buried,Buried,Exposed,Exposed,Exposed</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
         <is>
           <t>Tetradecameric mitochondrial chaperonin; required for ATP-dependent folding of precursor polypeptides and complex assembly; prevents aggregation and mediates protein refolding after heat shock; role in mtDNA transmission; phosphorylated</t>
         </is>
@@ -3369,20 +3189,15 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
+          <t>83.44,50.92,51.53,31.29,23.53,1.75,4.31,45.45,33.57,22.09,17.48,22.7,1.23,0,11.89,0,36.36,31.29,31.47,0,0,1.18,38.46,27.06,25.87,41.26,2.45,40,51.05,73.01,73.01,46.27,40,13.99,0,47.24,16.08,51.05,55.21</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
           <t>Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Buried,Exposed,Exposed,Exposed,Buried,Exposed,Buried,Buried,Buried,Buried,Exposed,Exposed,Exposed,Buried,Buried,Buried,Exposed,Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Buried,Exposed,Buried,Exposed,Exposed</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>83.44,50.92,51.53,31.29,23.53,1.75,4.31,45.45,33.57,22.09,17.48,22.7,1.23,0,11.89,0,36.36,31.29,31.47,0,0,1.18,38.46,27.06,25.87,41.26,2.45,40,51.05,73.01,73.01,46.27,40,13.99,0,47.24,16.08,51.05,55.21</t>
-        </is>
-      </c>
       <c r="O37" t="inlineStr">
-        <is>
-          <t>Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Buried,Exposed,Exposed,Exposed,Buried,Exposed,Buried,Buried,Buried,Buried,Exposed,Exposed,Exposed,Buried,Buried,Buried,Exposed,Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Buried,Exposed,Buried,Exposed,Exposed</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
         <is>
           <t>Acetohydroxyacid reductoisomerase and mtDNA binding protein; involved in branched-chain amino acid biosynthesis and maintenance of wild-type mitochondrial DNA; found in mitochondrial nucleoids</t>
         </is>
@@ -3451,20 +3266,15 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
+          <t>75.52,76.22,79.72,61.54,70.63,60.74,25.17,26.57,19.63,1.84,4.9,10.43,6.75,76.22,9.02,42.94,2.1,0,6.29,0.61,71.17,55.37,0.51,66.87,0,33.57,33.74,65.73,2.1,62.94,19.58,32.52,28.67,42.94,34.27,46.01,29.45,9.09,26.57,28.67,13.5,14.69,6.99,52.45,90.91</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
           <t>Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Buried,Buried,Buried,Buried,Exposed,Buried,Exposed,Buried,Buried,Buried,Buried,Exposed,Exposed,Buried,Exposed,Buried,Exposed,Exposed,Exposed,Buried,Exposed,Buried,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Buried,Buried,Buried,Exposed,Exposed</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>75.52,76.22,79.72,61.54,70.63,60.74,25.17,26.57,19.63,1.84,4.9,10.43,6.75,76.22,9.02,42.94,2.1,0,6.29,0.61,71.17,55.37,0.51,66.87,0,33.57,33.74,65.73,2.1,62.94,19.58,32.52,28.67,42.94,34.27,46.01,29.45,9.09,26.57,28.67,13.5,14.69,6.99,52.45,90.91</t>
-        </is>
-      </c>
       <c r="O38" t="inlineStr">
-        <is>
-          <t>Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Buried,Buried,Buried,Buried,Exposed,Buried,Exposed,Buried,Buried,Buried,Buried,Exposed,Exposed,Buried,Exposed,Buried,Exposed,Exposed,Exposed,Buried,Exposed,Buried,Exposed,Exposed,Exposed,Exposed,Exposed,Exposed,Buried,Exposed,Exposed,Buried,Buried,Buried,Exposed,Exposed</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
         <is>
           <t>Hsp70 family ATPase; constituent of the import motor component of the Translocase of the Inner Mitochondrial membrane (TIM23 complex); involved in protein translocation and folding; subunit of SceI endonuclease; SSC1 has a paralog, ECM10, that arose from the whole genome duplication</t>
         </is>
